--- a/data/dados_tratados_lrcap26_ute_uhe_input_analistas.xlsx
+++ b/data/dados_tratados_lrcap26_ute_uhe_input_analistas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://onsbr-my.sharepoint.com/personal/hugo_muzitano_ons_org_br1/Documents/_ONS Pessoal/06_Projetos R/app_lrcap2026_utes_uhes/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://onsbr-my.sharepoint.com/personal/hugo_muzitano_ons_org_br1/Documents/Arquivos de Chat do Microsoft Teams/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="96" documentId="11_D29FDFCF8F79A8D366075C52F37BD2722A4F345B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6A4569D0-3840-4724-93F7-BCADF376E069}"/>
+  <xr:revisionPtr revIDLastSave="124" documentId="11_D29FDFCF8F79A8D366075C52F37BD2722A4F345B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CDFAC725-EA18-45F5-B3CB-0FF17B817B68}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5758" uniqueCount="1226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5755" uniqueCount="1225">
   <si>
     <t>nom_leilao</t>
   </si>
@@ -3694,13 +3694,10 @@
     <t>Usina existente de 87,048 MW de potência instalada cadastrada para os produtos 2026, 2027, 2028, 2029, 2030 e 2031 (UTE Juiz de Forapossui delta de 1,5 MW  entre o MUSDg e máxima  potência injetável).</t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
     <t>Apesar de se tratarem de dois cadastros, foi confirmado junto à EPE que devem ser considerados como um único empreendimento.</t>
   </si>
   <si>
-    <t>Devemos verificar se os outros dois projetos se tratam desse mesmos segregado ou não.</t>
+    <t>Esse projeto corresponde à unificação dos outros dois projetos no mesmo ponto.</t>
   </si>
 </sst>
 </file>
@@ -3724,7 +3721,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3734,12 +3731,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4FBAF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3771,7 +3762,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3796,9 +3787,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4110,38 +4098,38 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AE386"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="22.1796875" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.90625" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.1796875" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.21875" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="27.90625" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="34.36328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="63.08984375" style="2" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="22.26953125" style="2" customWidth="1"/>
-    <col min="9" max="9" width="18.08984375" style="2" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="67.90625" style="2" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="26.1796875" style="2" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="18.54296875" style="2" hidden="1" customWidth="1"/>
-    <col min="13" max="13" width="31.08984375" style="2" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="30.6328125" style="2" hidden="1" customWidth="1"/>
-    <col min="15" max="15" width="21.90625" style="2" hidden="1" customWidth="1"/>
-    <col min="16" max="16" width="23.81640625" style="2" hidden="1" customWidth="1"/>
-    <col min="17" max="17" width="15.81640625" style="2" hidden="1" customWidth="1"/>
-    <col min="18" max="18" width="20.54296875" style="2" hidden="1" customWidth="1"/>
-    <col min="19" max="19" width="36.81640625" style="2" hidden="1" customWidth="1"/>
-    <col min="20" max="20" width="20.26953125" style="2" hidden="1" customWidth="1"/>
-    <col min="21" max="21" width="63.6328125" style="2" hidden="1" customWidth="1"/>
-    <col min="22" max="22" width="23.26953125" style="2" hidden="1" customWidth="1"/>
-    <col min="23" max="23" width="9.36328125" style="2" hidden="1" customWidth="1"/>
-    <col min="24" max="28" width="9.36328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="25.90625" style="2" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="23.1796875" style="2" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="43.7265625" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="27.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="34.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="63.109375" style="2" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="39.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.109375" style="2" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="67.88671875" style="2" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="26.21875" style="2" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="18.5546875" style="2" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="31.109375" style="2" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="30.6640625" style="2" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="21.88671875" style="2" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="23.77734375" style="2" hidden="1" customWidth="1"/>
+    <col min="17" max="17" width="15.77734375" style="2" hidden="1" customWidth="1"/>
+    <col min="18" max="18" width="20.5546875" style="2" hidden="1" customWidth="1"/>
+    <col min="19" max="19" width="36.77734375" style="2" hidden="1" customWidth="1"/>
+    <col min="20" max="20" width="20.21875" style="2" hidden="1" customWidth="1"/>
+    <col min="21" max="21" width="63.6640625" style="2" hidden="1" customWidth="1"/>
+    <col min="22" max="22" width="23.21875" style="2" hidden="1" customWidth="1"/>
+    <col min="23" max="23" width="9.33203125" style="2" hidden="1" customWidth="1"/>
+    <col min="24" max="28" width="9.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="25.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="23.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="43.77734375" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" s="1" customFormat="1" ht="38.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:31" s="1" customFormat="1" ht="38.549999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -4236,7 +4224,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>30</v>
       </c>
@@ -4309,7 +4297,7 @@
       <c r="AD2" s="7"/>
       <c r="AE2" s="8"/>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>30</v>
       </c>
@@ -4384,7 +4372,7 @@
       <c r="AD3" s="7"/>
       <c r="AE3" s="8"/>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
         <v>30</v>
       </c>
@@ -4459,7 +4447,7 @@
       <c r="AD4" s="7"/>
       <c r="AE4" s="8"/>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
         <v>30</v>
       </c>
@@ -4532,7 +4520,7 @@
       <c r="AD5" s="7"/>
       <c r="AE5" s="8"/>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
         <v>30</v>
       </c>
@@ -4605,7 +4593,7 @@
       <c r="AD6" s="7"/>
       <c r="AE6" s="8"/>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
         <v>30</v>
       </c>
@@ -4678,7 +4666,7 @@
       <c r="AD7" s="7"/>
       <c r="AE7" s="8"/>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
         <v>30</v>
       </c>
@@ -4751,7 +4739,7 @@
       <c r="AD8" s="7"/>
       <c r="AE8" s="8"/>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
         <v>30</v>
       </c>
@@ -4824,7 +4812,7 @@
       <c r="AD9" s="7"/>
       <c r="AE9" s="8"/>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
         <v>30</v>
       </c>
@@ -4897,7 +4885,7 @@
       <c r="AD10" s="7"/>
       <c r="AE10" s="8"/>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
         <v>30</v>
       </c>
@@ -4970,7 +4958,7 @@
       <c r="AD11" s="7"/>
       <c r="AE11" s="8"/>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
         <v>30</v>
       </c>
@@ -5043,7 +5031,7 @@
       <c r="AD12" s="7"/>
       <c r="AE12" s="8"/>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
         <v>30</v>
       </c>
@@ -5116,7 +5104,7 @@
       <c r="AD13" s="7"/>
       <c r="AE13" s="8"/>
     </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
         <v>30</v>
       </c>
@@ -5189,7 +5177,7 @@
       <c r="AD14" s="7"/>
       <c r="AE14" s="8"/>
     </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
         <v>30</v>
       </c>
@@ -5262,7 +5250,7 @@
       <c r="AD15" s="7"/>
       <c r="AE15" s="8"/>
     </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
         <v>30</v>
       </c>
@@ -5335,7 +5323,7 @@
       <c r="AD16" s="7"/>
       <c r="AE16" s="8"/>
     </row>
-    <row r="17" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
         <v>30</v>
       </c>
@@ -5412,7 +5400,7 @@
       <c r="AD17" s="7"/>
       <c r="AE17" s="8"/>
     </row>
-    <row r="18" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
         <v>30</v>
       </c>
@@ -5491,7 +5479,7 @@
       <c r="AD18" s="7"/>
       <c r="AE18" s="8"/>
     </row>
-    <row r="19" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A19" s="6" t="s">
         <v>30</v>
       </c>
@@ -5562,7 +5550,7 @@
       <c r="AD19" s="7"/>
       <c r="AE19" s="8"/>
     </row>
-    <row r="20" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
         <v>30</v>
       </c>
@@ -5641,7 +5629,7 @@
       <c r="AD20" s="7"/>
       <c r="AE20" s="8"/>
     </row>
-    <row r="21" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
         <v>30</v>
       </c>
@@ -5716,7 +5704,7 @@
       <c r="AD21" s="7"/>
       <c r="AE21" s="8"/>
     </row>
-    <row r="22" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
         <v>30</v>
       </c>
@@ -5791,7 +5779,7 @@
       <c r="AD22" s="7"/>
       <c r="AE22" s="8"/>
     </row>
-    <row r="23" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A23" s="6" t="s">
         <v>30</v>
       </c>
@@ -5866,7 +5854,7 @@
       <c r="AD23" s="7"/>
       <c r="AE23" s="8"/>
     </row>
-    <row r="24" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A24" s="6" t="s">
         <v>30</v>
       </c>
@@ -5939,7 +5927,7 @@
       <c r="AD24" s="7"/>
       <c r="AE24" s="8"/>
     </row>
-    <row r="25" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A25" s="6" t="s">
         <v>30</v>
       </c>
@@ -6014,7 +6002,7 @@
       <c r="AD25" s="7"/>
       <c r="AE25" s="8"/>
     </row>
-    <row r="26" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A26" s="6" t="s">
         <v>117</v>
       </c>
@@ -6083,7 +6071,7 @@
       <c r="AD26" s="7"/>
       <c r="AE26" s="8"/>
     </row>
-    <row r="27" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A27" s="6" t="s">
         <v>117</v>
       </c>
@@ -6154,7 +6142,7 @@
       <c r="AD27" s="7"/>
       <c r="AE27" s="8"/>
     </row>
-    <row r="28" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A28" s="6" t="s">
         <v>30</v>
       </c>
@@ -6227,7 +6215,7 @@
       <c r="AD28" s="7"/>
       <c r="AE28" s="8"/>
     </row>
-    <row r="29" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A29" s="6" t="s">
         <v>30</v>
       </c>
@@ -6302,7 +6290,7 @@
       <c r="AD29" s="7"/>
       <c r="AE29" s="8"/>
     </row>
-    <row r="30" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A30" s="6" t="s">
         <v>30</v>
       </c>
@@ -6377,7 +6365,7 @@
       <c r="AD30" s="7"/>
       <c r="AE30" s="8"/>
     </row>
-    <row r="31" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A31" s="6" t="s">
         <v>30</v>
       </c>
@@ -6452,7 +6440,7 @@
       <c r="AD31" s="7"/>
       <c r="AE31" s="8"/>
     </row>
-    <row r="32" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A32" s="6" t="s">
         <v>117</v>
       </c>
@@ -6521,7 +6509,7 @@
       <c r="AD32" s="7"/>
       <c r="AE32" s="8"/>
     </row>
-    <row r="33" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A33" s="6" t="s">
         <v>30</v>
       </c>
@@ -6594,7 +6582,7 @@
       <c r="AD33" s="7"/>
       <c r="AE33" s="8"/>
     </row>
-    <row r="34" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A34" s="6" t="s">
         <v>117</v>
       </c>
@@ -6665,7 +6653,7 @@
       <c r="AD34" s="7"/>
       <c r="AE34" s="8"/>
     </row>
-    <row r="35" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A35" s="6" t="s">
         <v>117</v>
       </c>
@@ -6736,7 +6724,7 @@
       <c r="AD35" s="7"/>
       <c r="AE35" s="8"/>
     </row>
-    <row r="36" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A36" s="6" t="s">
         <v>117</v>
       </c>
@@ -6807,7 +6795,7 @@
       <c r="AD36" s="7"/>
       <c r="AE36" s="8"/>
     </row>
-    <row r="37" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A37" s="6" t="s">
         <v>30</v>
       </c>
@@ -6888,7 +6876,7 @@
       <c r="AD37" s="7"/>
       <c r="AE37" s="8"/>
     </row>
-    <row r="38" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A38" s="6" t="s">
         <v>30</v>
       </c>
@@ -6955,7 +6943,7 @@
       <c r="AD38" s="7"/>
       <c r="AE38" s="8"/>
     </row>
-    <row r="39" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A39" s="6" t="s">
         <v>30</v>
       </c>
@@ -7028,7 +7016,7 @@
       <c r="AD39" s="7"/>
       <c r="AE39" s="8"/>
     </row>
-    <row r="40" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A40" s="6" t="s">
         <v>30</v>
       </c>
@@ -7101,7 +7089,7 @@
       <c r="AD40" s="7"/>
       <c r="AE40" s="8"/>
     </row>
-    <row r="41" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A41" s="6" t="s">
         <v>30</v>
       </c>
@@ -7174,7 +7162,7 @@
       <c r="AD41" s="7"/>
       <c r="AE41" s="8"/>
     </row>
-    <row r="42" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A42" s="6" t="s">
         <v>30</v>
       </c>
@@ -7247,7 +7235,7 @@
       <c r="AD42" s="7"/>
       <c r="AE42" s="8"/>
     </row>
-    <row r="43" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A43" s="6" t="s">
         <v>30</v>
       </c>
@@ -7320,7 +7308,7 @@
       <c r="AD43" s="7"/>
       <c r="AE43" s="8"/>
     </row>
-    <row r="44" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A44" s="6" t="s">
         <v>30</v>
       </c>
@@ -7395,7 +7383,7 @@
       <c r="AD44" s="7"/>
       <c r="AE44" s="8"/>
     </row>
-    <row r="45" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A45" s="6" t="s">
         <v>30</v>
       </c>
@@ -7470,7 +7458,7 @@
       <c r="AD45" s="7"/>
       <c r="AE45" s="8"/>
     </row>
-    <row r="46" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A46" s="6" t="s">
         <v>30</v>
       </c>
@@ -7545,7 +7533,7 @@
       <c r="AD46" s="7"/>
       <c r="AE46" s="8"/>
     </row>
-    <row r="47" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A47" s="6" t="s">
         <v>30</v>
       </c>
@@ -7618,7 +7606,7 @@
       <c r="AD47" s="7"/>
       <c r="AE47" s="8"/>
     </row>
-    <row r="48" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A48" s="6" t="s">
         <v>30</v>
       </c>
@@ -7691,7 +7679,7 @@
       <c r="AD48" s="7"/>
       <c r="AE48" s="8"/>
     </row>
-    <row r="49" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A49" s="6" t="s">
         <v>30</v>
       </c>
@@ -7762,7 +7750,7 @@
       <c r="AD49" s="7"/>
       <c r="AE49" s="8"/>
     </row>
-    <row r="50" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A50" s="6" t="s">
         <v>30</v>
       </c>
@@ -7835,7 +7823,7 @@
       <c r="AD50" s="7"/>
       <c r="AE50" s="8"/>
     </row>
-    <row r="51" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A51" s="6" t="s">
         <v>30</v>
       </c>
@@ -7908,7 +7896,7 @@
       <c r="AD51" s="7"/>
       <c r="AE51" s="8"/>
     </row>
-    <row r="52" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A52" s="6" t="s">
         <v>30</v>
       </c>
@@ -7981,7 +7969,7 @@
       <c r="AD52" s="7"/>
       <c r="AE52" s="8"/>
     </row>
-    <row r="53" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A53" s="6" t="s">
         <v>30</v>
       </c>
@@ -8054,7 +8042,7 @@
       <c r="AD53" s="7"/>
       <c r="AE53" s="8"/>
     </row>
-    <row r="54" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A54" s="6" t="s">
         <v>30</v>
       </c>
@@ -8127,7 +8115,7 @@
       <c r="AD54" s="7"/>
       <c r="AE54" s="8"/>
     </row>
-    <row r="55" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A55" s="6" t="s">
         <v>30</v>
       </c>
@@ -8200,7 +8188,7 @@
       <c r="AD55" s="7"/>
       <c r="AE55" s="8"/>
     </row>
-    <row r="56" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A56" s="6" t="s">
         <v>30</v>
       </c>
@@ -8273,7 +8261,7 @@
       <c r="AD56" s="7"/>
       <c r="AE56" s="8"/>
     </row>
-    <row r="57" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A57" s="6" t="s">
         <v>30</v>
       </c>
@@ -8346,7 +8334,7 @@
       <c r="AD57" s="7"/>
       <c r="AE57" s="8"/>
     </row>
-    <row r="58" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A58" s="6" t="s">
         <v>30</v>
       </c>
@@ -8421,7 +8409,7 @@
       <c r="AD58" s="7"/>
       <c r="AE58" s="8"/>
     </row>
-    <row r="59" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A59" s="6" t="s">
         <v>30</v>
       </c>
@@ -8494,7 +8482,7 @@
       <c r="AD59" s="7"/>
       <c r="AE59" s="8"/>
     </row>
-    <row r="60" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A60" s="6" t="s">
         <v>30</v>
       </c>
@@ -8567,7 +8555,7 @@
       <c r="AD60" s="7"/>
       <c r="AE60" s="8"/>
     </row>
-    <row r="61" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A61" s="6" t="s">
         <v>30</v>
       </c>
@@ -8640,7 +8628,7 @@
       <c r="AD61" s="7"/>
       <c r="AE61" s="8"/>
     </row>
-    <row r="62" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A62" s="6" t="s">
         <v>117</v>
       </c>
@@ -8709,7 +8697,7 @@
       <c r="AD62" s="7"/>
       <c r="AE62" s="8"/>
     </row>
-    <row r="63" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A63" s="6" t="s">
         <v>117</v>
       </c>
@@ -8778,7 +8766,7 @@
       <c r="AD63" s="7"/>
       <c r="AE63" s="8"/>
     </row>
-    <row r="64" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A64" s="6" t="s">
         <v>117</v>
       </c>
@@ -8847,7 +8835,7 @@
       <c r="AD64" s="7"/>
       <c r="AE64" s="8"/>
     </row>
-    <row r="65" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A65" s="6" t="s">
         <v>30</v>
       </c>
@@ -8920,7 +8908,7 @@
       <c r="AD65" s="7"/>
       <c r="AE65" s="8"/>
     </row>
-    <row r="66" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A66" s="6" t="s">
         <v>30</v>
       </c>
@@ -8993,7 +8981,7 @@
       <c r="AD66" s="7"/>
       <c r="AE66" s="8"/>
     </row>
-    <row r="67" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A67" s="6" t="s">
         <v>30</v>
       </c>
@@ -9066,7 +9054,7 @@
       <c r="AD67" s="7"/>
       <c r="AE67" s="8"/>
     </row>
-    <row r="68" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A68" s="6" t="s">
         <v>117</v>
       </c>
@@ -9137,7 +9125,7 @@
       <c r="AD68" s="7"/>
       <c r="AE68" s="8"/>
     </row>
-    <row r="69" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A69" s="6" t="s">
         <v>117</v>
       </c>
@@ -9210,7 +9198,7 @@
       <c r="AD69" s="7"/>
       <c r="AE69" s="8"/>
     </row>
-    <row r="70" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A70" s="6" t="s">
         <v>30</v>
       </c>
@@ -9291,7 +9279,7 @@
       <c r="AD70" s="7"/>
       <c r="AE70" s="8"/>
     </row>
-    <row r="71" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A71" s="6" t="s">
         <v>30</v>
       </c>
@@ -9372,7 +9360,7 @@
       <c r="AD71" s="7"/>
       <c r="AE71" s="8"/>
     </row>
-    <row r="72" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A72" s="6" t="s">
         <v>30</v>
       </c>
@@ -9451,7 +9439,7 @@
       <c r="AD72" s="7"/>
       <c r="AE72" s="8"/>
     </row>
-    <row r="73" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A73" s="6" t="s">
         <v>30</v>
       </c>
@@ -9524,7 +9512,7 @@
       <c r="AD73" s="7"/>
       <c r="AE73" s="8"/>
     </row>
-    <row r="74" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A74" s="6" t="s">
         <v>30</v>
       </c>
@@ -9597,7 +9585,7 @@
       <c r="AD74" s="7"/>
       <c r="AE74" s="8"/>
     </row>
-    <row r="75" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A75" s="6" t="s">
         <v>30</v>
       </c>
@@ -9670,7 +9658,7 @@
       <c r="AD75" s="7"/>
       <c r="AE75" s="8"/>
     </row>
-    <row r="76" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A76" s="6" t="s">
         <v>30</v>
       </c>
@@ -9743,7 +9731,7 @@
       <c r="AD76" s="7"/>
       <c r="AE76" s="8"/>
     </row>
-    <row r="77" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A77" s="6" t="s">
         <v>30</v>
       </c>
@@ -9816,7 +9804,7 @@
       <c r="AD77" s="7"/>
       <c r="AE77" s="8"/>
     </row>
-    <row r="78" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A78" s="6" t="s">
         <v>30</v>
       </c>
@@ -9893,7 +9881,7 @@
       <c r="AD78" s="7"/>
       <c r="AE78" s="8"/>
     </row>
-    <row r="79" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A79" s="6" t="s">
         <v>30</v>
       </c>
@@ -9966,7 +9954,7 @@
       <c r="AD79" s="7"/>
       <c r="AE79" s="8"/>
     </row>
-    <row r="80" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A80" s="6" t="s">
         <v>30</v>
       </c>
@@ -10041,7 +10029,7 @@
       <c r="AD80" s="7"/>
       <c r="AE80" s="8"/>
     </row>
-    <row r="81" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A81" s="6" t="s">
         <v>30</v>
       </c>
@@ -10116,7 +10104,7 @@
       <c r="AD81" s="7"/>
       <c r="AE81" s="8"/>
     </row>
-    <row r="82" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A82" s="6" t="s">
         <v>30</v>
       </c>
@@ -10191,7 +10179,7 @@
       <c r="AD82" s="7"/>
       <c r="AE82" s="8"/>
     </row>
-    <row r="83" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A83" s="6" t="s">
         <v>117</v>
       </c>
@@ -10260,7 +10248,7 @@
       <c r="AD83" s="7"/>
       <c r="AE83" s="8"/>
     </row>
-    <row r="84" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A84" s="6" t="s">
         <v>117</v>
       </c>
@@ -10331,7 +10319,7 @@
       <c r="AD84" s="7"/>
       <c r="AE84" s="8"/>
     </row>
-    <row r="85" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A85" s="6" t="s">
         <v>30</v>
       </c>
@@ -10412,7 +10400,7 @@
       <c r="AD85" s="7"/>
       <c r="AE85" s="8"/>
     </row>
-    <row r="86" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A86" s="6" t="s">
         <v>30</v>
       </c>
@@ -10491,7 +10479,7 @@
       <c r="AD86" s="7"/>
       <c r="AE86" s="8"/>
     </row>
-    <row r="87" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A87" s="6" t="s">
         <v>30</v>
       </c>
@@ -10572,7 +10560,7 @@
       <c r="AD87" s="7"/>
       <c r="AE87" s="8"/>
     </row>
-    <row r="88" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A88" s="6" t="s">
         <v>30</v>
       </c>
@@ -10645,7 +10633,7 @@
       <c r="AD88" s="7"/>
       <c r="AE88" s="8"/>
     </row>
-    <row r="89" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A89" s="6" t="s">
         <v>30</v>
       </c>
@@ -10718,7 +10706,7 @@
       <c r="AD89" s="7"/>
       <c r="AE89" s="8"/>
     </row>
-    <row r="90" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A90" s="6" t="s">
         <v>30</v>
       </c>
@@ -10791,7 +10779,7 @@
       <c r="AD90" s="7"/>
       <c r="AE90" s="8"/>
     </row>
-    <row r="91" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A91" s="6" t="s">
         <v>30</v>
       </c>
@@ -10864,7 +10852,7 @@
       <c r="AD91" s="7"/>
       <c r="AE91" s="8"/>
     </row>
-    <row r="92" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A92" s="6" t="s">
         <v>30</v>
       </c>
@@ -10941,7 +10929,7 @@
       <c r="AD92" s="7"/>
       <c r="AE92" s="8"/>
     </row>
-    <row r="93" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A93" s="6" t="s">
         <v>30</v>
       </c>
@@ -11018,7 +11006,7 @@
       <c r="AD93" s="7"/>
       <c r="AE93" s="8"/>
     </row>
-    <row r="94" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A94" s="6" t="s">
         <v>30</v>
       </c>
@@ -11095,7 +11083,7 @@
       <c r="AD94" s="7"/>
       <c r="AE94" s="8"/>
     </row>
-    <row r="95" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A95" s="6" t="s">
         <v>30</v>
       </c>
@@ -11172,7 +11160,7 @@
       <c r="AD95" s="7"/>
       <c r="AE95" s="8"/>
     </row>
-    <row r="96" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A96" s="6" t="s">
         <v>30</v>
       </c>
@@ -11245,7 +11233,7 @@
       <c r="AD96" s="7"/>
       <c r="AE96" s="8"/>
     </row>
-    <row r="97" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A97" s="6" t="s">
         <v>30</v>
       </c>
@@ -11318,7 +11306,7 @@
       <c r="AD97" s="7"/>
       <c r="AE97" s="8"/>
     </row>
-    <row r="98" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A98" s="6" t="s">
         <v>30</v>
       </c>
@@ -11391,7 +11379,7 @@
       <c r="AD98" s="7"/>
       <c r="AE98" s="8"/>
     </row>
-    <row r="99" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A99" s="6" t="s">
         <v>30</v>
       </c>
@@ -11466,7 +11454,7 @@
       <c r="AD99" s="7"/>
       <c r="AE99" s="8"/>
     </row>
-    <row r="100" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A100" s="6" t="s">
         <v>30</v>
       </c>
@@ -11541,7 +11529,7 @@
       <c r="AD100" s="7"/>
       <c r="AE100" s="8"/>
     </row>
-    <row r="101" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A101" s="6" t="s">
         <v>30</v>
       </c>
@@ -11616,7 +11604,7 @@
       <c r="AD101" s="7"/>
       <c r="AE101" s="8"/>
     </row>
-    <row r="102" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A102" s="6" t="s">
         <v>30</v>
       </c>
@@ -11693,7 +11681,7 @@
       <c r="AD102" s="7"/>
       <c r="AE102" s="8"/>
     </row>
-    <row r="103" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A103" s="6" t="s">
         <v>30</v>
       </c>
@@ -11766,7 +11754,7 @@
       <c r="AD103" s="7"/>
       <c r="AE103" s="8"/>
     </row>
-    <row r="104" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A104" s="6" t="s">
         <v>30</v>
       </c>
@@ -11839,7 +11827,7 @@
       <c r="AD104" s="7"/>
       <c r="AE104" s="8"/>
     </row>
-    <row r="105" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A105" s="6" t="s">
         <v>30</v>
       </c>
@@ -11912,7 +11900,7 @@
       <c r="AD105" s="7"/>
       <c r="AE105" s="8"/>
     </row>
-    <row r="106" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A106" s="6" t="s">
         <v>30</v>
       </c>
@@ -11985,7 +11973,7 @@
       <c r="AD106" s="7"/>
       <c r="AE106" s="8"/>
     </row>
-    <row r="107" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A107" s="6" t="s">
         <v>30</v>
       </c>
@@ -12058,7 +12046,7 @@
       <c r="AD107" s="7"/>
       <c r="AE107" s="8"/>
     </row>
-    <row r="108" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A108" s="6" t="s">
         <v>30</v>
       </c>
@@ -12131,7 +12119,7 @@
       <c r="AD108" s="7"/>
       <c r="AE108" s="8"/>
     </row>
-    <row r="109" spans="1:31" ht="58" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:31" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A109" s="6" t="s">
         <v>117</v>
       </c>
@@ -12206,7 +12194,7 @@
         <v>1220</v>
       </c>
     </row>
-    <row r="110" spans="1:31" ht="58" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:31" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A110" s="6" t="s">
         <v>117</v>
       </c>
@@ -12279,7 +12267,7 @@
         <v>1219</v>
       </c>
     </row>
-    <row r="111" spans="1:31" ht="87" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:31" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A111" s="6" t="s">
         <v>117</v>
       </c>
@@ -12344,8 +12332,8 @@
         <v>41</v>
       </c>
       <c r="AB111" s="6"/>
-      <c r="AC111" s="7" t="s">
-        <v>1223</v>
+      <c r="AC111" s="7">
+        <v>0</v>
       </c>
       <c r="AD111" s="7" t="s">
         <v>1216</v>
@@ -12354,7 +12342,7 @@
         <v>1218</v>
       </c>
     </row>
-    <row r="112" spans="1:31" ht="87" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:31" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A112" s="6" t="s">
         <v>117</v>
       </c>
@@ -12417,8 +12405,8 @@
         <v>41</v>
       </c>
       <c r="AB112" s="6"/>
-      <c r="AC112" s="7" t="s">
-        <v>1223</v>
+      <c r="AC112" s="7">
+        <v>0</v>
       </c>
       <c r="AD112" s="7" t="s">
         <v>1216</v>
@@ -12427,7 +12415,7 @@
         <v>1218</v>
       </c>
     </row>
-    <row r="113" spans="1:31" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:31" ht="72" x14ac:dyDescent="0.3">
       <c r="A113" s="6" t="s">
         <v>30</v>
       </c>
@@ -12502,7 +12490,7 @@
         <v>1217</v>
       </c>
     </row>
-    <row r="114" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A114" s="6" t="s">
         <v>30</v>
       </c>
@@ -12581,7 +12569,7 @@
       <c r="AD114" s="7"/>
       <c r="AE114" s="8"/>
     </row>
-    <row r="115" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A115" s="6" t="s">
         <v>30</v>
       </c>
@@ -12654,7 +12642,7 @@
       <c r="AD115" s="7"/>
       <c r="AE115" s="8"/>
     </row>
-    <row r="116" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A116" s="6" t="s">
         <v>30</v>
       </c>
@@ -12727,7 +12715,7 @@
       <c r="AD116" s="7"/>
       <c r="AE116" s="8"/>
     </row>
-    <row r="117" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A117" s="6" t="s">
         <v>30</v>
       </c>
@@ -12802,7 +12790,7 @@
       <c r="AD117" s="7"/>
       <c r="AE117" s="8"/>
     </row>
-    <row r="118" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A118" s="6" t="s">
         <v>30</v>
       </c>
@@ -12877,7 +12865,7 @@
       <c r="AD118" s="7"/>
       <c r="AE118" s="8"/>
     </row>
-    <row r="119" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A119" s="6" t="s">
         <v>30</v>
       </c>
@@ -12952,7 +12940,7 @@
       <c r="AD119" s="7"/>
       <c r="AE119" s="8"/>
     </row>
-    <row r="120" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A120" s="6" t="s">
         <v>30</v>
       </c>
@@ -13029,7 +13017,7 @@
       <c r="AD120" s="7"/>
       <c r="AE120" s="8"/>
     </row>
-    <row r="121" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A121" s="6" t="s">
         <v>30</v>
       </c>
@@ -13104,7 +13092,7 @@
       <c r="AD121" s="7"/>
       <c r="AE121" s="8"/>
     </row>
-    <row r="122" spans="1:31" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:31" ht="72" x14ac:dyDescent="0.3">
       <c r="A122" s="6" t="s">
         <v>30</v>
       </c>
@@ -13187,7 +13175,7 @@
         <v>1222</v>
       </c>
     </row>
-    <row r="123" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A123" s="6" t="s">
         <v>30</v>
       </c>
@@ -13258,7 +13246,7 @@
       <c r="AD123" s="7"/>
       <c r="AE123" s="8"/>
     </row>
-    <row r="124" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A124" s="6" t="s">
         <v>30</v>
       </c>
@@ -13331,7 +13319,7 @@
       <c r="AD124" s="7"/>
       <c r="AE124" s="8"/>
     </row>
-    <row r="125" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A125" s="6" t="s">
         <v>30</v>
       </c>
@@ -13404,7 +13392,7 @@
       <c r="AD125" s="7"/>
       <c r="AE125" s="8"/>
     </row>
-    <row r="126" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A126" s="6" t="s">
         <v>30</v>
       </c>
@@ -13416,7 +13404,7 @@
       </c>
       <c r="D126" s="6"/>
       <c r="E126" s="6" t="s">
-        <v>449</v>
+        <v>1128</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>450</v>
@@ -13480,12 +13468,12 @@
         <v>41</v>
       </c>
       <c r="AC126" s="7">
-        <v>249</v>
+        <v>0</v>
       </c>
       <c r="AD126" s="7"/>
       <c r="AE126" s="8"/>
     </row>
-    <row r="127" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A127" s="6" t="s">
         <v>30</v>
       </c>
@@ -13560,7 +13548,7 @@
       <c r="AD127" s="7"/>
       <c r="AE127" s="8"/>
     </row>
-    <row r="128" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A128" s="6" t="s">
         <v>30</v>
       </c>
@@ -13633,7 +13621,7 @@
       <c r="AD128" s="7"/>
       <c r="AE128" s="8"/>
     </row>
-    <row r="129" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A129" s="6" t="s">
         <v>30</v>
       </c>
@@ -13706,7 +13694,7 @@
       <c r="AD129" s="7"/>
       <c r="AE129" s="8"/>
     </row>
-    <row r="130" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A130" s="6" t="s">
         <v>30</v>
       </c>
@@ -13779,7 +13767,7 @@
       <c r="AD130" s="7"/>
       <c r="AE130" s="8"/>
     </row>
-    <row r="131" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A131" s="6" t="s">
         <v>30</v>
       </c>
@@ -13852,7 +13840,7 @@
       <c r="AD131" s="7"/>
       <c r="AE131" s="8"/>
     </row>
-    <row r="132" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A132" s="6" t="s">
         <v>30</v>
       </c>
@@ -13923,7 +13911,7 @@
       <c r="AD132" s="7"/>
       <c r="AE132" s="8"/>
     </row>
-    <row r="133" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A133" s="6" t="s">
         <v>30</v>
       </c>
@@ -13935,7 +13923,7 @@
       </c>
       <c r="D133" s="6"/>
       <c r="E133" s="6" t="s">
-        <v>449</v>
+        <v>1128</v>
       </c>
       <c r="F133" s="6" t="s">
         <v>478</v>
@@ -13996,7 +13984,7 @@
       <c r="AD133" s="7"/>
       <c r="AE133" s="8"/>
     </row>
-    <row r="134" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A134" s="6" t="s">
         <v>30</v>
       </c>
@@ -14069,7 +14057,7 @@
       <c r="AD134" s="7"/>
       <c r="AE134" s="8"/>
     </row>
-    <row r="135" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A135" s="6" t="s">
         <v>30</v>
       </c>
@@ -14142,7 +14130,7 @@
       <c r="AD135" s="7"/>
       <c r="AE135" s="8"/>
     </row>
-    <row r="136" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A136" s="6" t="s">
         <v>30</v>
       </c>
@@ -14215,7 +14203,7 @@
       <c r="AD136" s="7"/>
       <c r="AE136" s="8"/>
     </row>
-    <row r="137" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A137" s="6" t="s">
         <v>30</v>
       </c>
@@ -14288,7 +14276,7 @@
       <c r="AD137" s="7"/>
       <c r="AE137" s="8"/>
     </row>
-    <row r="138" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A138" s="6" t="s">
         <v>117</v>
       </c>
@@ -14359,7 +14347,7 @@
       <c r="AD138" s="7"/>
       <c r="AE138" s="8"/>
     </row>
-    <row r="139" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A139" s="6" t="s">
         <v>117</v>
       </c>
@@ -14430,7 +14418,7 @@
       <c r="AD139" s="7"/>
       <c r="AE139" s="8"/>
     </row>
-    <row r="140" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A140" s="6" t="s">
         <v>30</v>
       </c>
@@ -14503,7 +14491,7 @@
       <c r="AD140" s="7"/>
       <c r="AE140" s="8"/>
     </row>
-    <row r="141" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A141" s="6" t="s">
         <v>30</v>
       </c>
@@ -14576,7 +14564,7 @@
       <c r="AD141" s="7"/>
       <c r="AE141" s="8"/>
     </row>
-    <row r="142" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A142" s="6" t="s">
         <v>30</v>
       </c>
@@ -14649,7 +14637,7 @@
       <c r="AD142" s="7"/>
       <c r="AE142" s="8"/>
     </row>
-    <row r="143" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A143" s="6" t="s">
         <v>30</v>
       </c>
@@ -14722,7 +14710,7 @@
       <c r="AD143" s="7"/>
       <c r="AE143" s="8"/>
     </row>
-    <row r="144" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A144" s="6" t="s">
         <v>30</v>
       </c>
@@ -14795,7 +14783,7 @@
       <c r="AD144" s="7"/>
       <c r="AE144" s="8"/>
     </row>
-    <row r="145" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A145" s="6" t="s">
         <v>30</v>
       </c>
@@ -14868,7 +14856,7 @@
       <c r="AD145" s="7"/>
       <c r="AE145" s="8"/>
     </row>
-    <row r="146" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A146" s="6" t="s">
         <v>30</v>
       </c>
@@ -14941,7 +14929,7 @@
       <c r="AD146" s="7"/>
       <c r="AE146" s="8"/>
     </row>
-    <row r="147" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A147" s="6" t="s">
         <v>30</v>
       </c>
@@ -15010,7 +14998,7 @@
       <c r="AD147" s="7"/>
       <c r="AE147" s="8"/>
     </row>
-    <row r="148" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A148" s="6" t="s">
         <v>30</v>
       </c>
@@ -15085,7 +15073,7 @@
       <c r="AD148" s="7"/>
       <c r="AE148" s="8"/>
     </row>
-    <row r="149" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A149" s="6" t="s">
         <v>117</v>
       </c>
@@ -15156,7 +15144,7 @@
       <c r="AD149" s="7"/>
       <c r="AE149" s="8"/>
     </row>
-    <row r="150" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A150" s="6" t="s">
         <v>117</v>
       </c>
@@ -15227,7 +15215,7 @@
       <c r="AD150" s="7"/>
       <c r="AE150" s="8"/>
     </row>
-    <row r="151" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A151" s="6" t="s">
         <v>117</v>
       </c>
@@ -15300,7 +15288,7 @@
       <c r="AD151" s="7"/>
       <c r="AE151" s="8"/>
     </row>
-    <row r="152" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A152" s="6" t="s">
         <v>30</v>
       </c>
@@ -15373,7 +15361,7 @@
       <c r="AD152" s="7"/>
       <c r="AE152" s="8"/>
     </row>
-    <row r="153" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A153" s="6" t="s">
         <v>30</v>
       </c>
@@ -15448,7 +15436,7 @@
       <c r="AD153" s="7"/>
       <c r="AE153" s="8"/>
     </row>
-    <row r="154" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A154" s="6" t="s">
         <v>30</v>
       </c>
@@ -15521,7 +15509,7 @@
       <c r="AD154" s="7"/>
       <c r="AE154" s="8"/>
     </row>
-    <row r="155" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A155" s="6" t="s">
         <v>30</v>
       </c>
@@ -15596,7 +15584,7 @@
       <c r="AD155" s="7"/>
       <c r="AE155" s="8"/>
     </row>
-    <row r="156" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A156" s="6" t="s">
         <v>30</v>
       </c>
@@ -15673,7 +15661,7 @@
       <c r="AD156" s="7"/>
       <c r="AE156" s="8"/>
     </row>
-    <row r="157" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A157" s="6" t="s">
         <v>30</v>
       </c>
@@ -15750,7 +15738,7 @@
       <c r="AD157" s="7"/>
       <c r="AE157" s="8"/>
     </row>
-    <row r="158" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A158" s="6" t="s">
         <v>117</v>
       </c>
@@ -15819,7 +15807,7 @@
       <c r="AD158" s="7"/>
       <c r="AE158" s="8"/>
     </row>
-    <row r="159" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A159" s="6" t="s">
         <v>117</v>
       </c>
@@ -15888,7 +15876,7 @@
       <c r="AD159" s="7"/>
       <c r="AE159" s="8"/>
     </row>
-    <row r="160" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A160" s="6" t="s">
         <v>117</v>
       </c>
@@ -15959,7 +15947,7 @@
       <c r="AD160" s="7"/>
       <c r="AE160" s="8"/>
     </row>
-    <row r="161" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A161" s="6" t="s">
         <v>117</v>
       </c>
@@ -16032,7 +16020,7 @@
       <c r="AD161" s="7"/>
       <c r="AE161" s="8"/>
     </row>
-    <row r="162" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A162" s="6" t="s">
         <v>117</v>
       </c>
@@ -16103,7 +16091,7 @@
       <c r="AD162" s="7"/>
       <c r="AE162" s="8"/>
     </row>
-    <row r="163" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A163" s="6" t="s">
         <v>117</v>
       </c>
@@ -16174,7 +16162,7 @@
       <c r="AD163" s="7"/>
       <c r="AE163" s="8"/>
     </row>
-    <row r="164" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A164" s="6" t="s">
         <v>30</v>
       </c>
@@ -16255,7 +16243,7 @@
       <c r="AD164" s="7"/>
       <c r="AE164" s="8"/>
     </row>
-    <row r="165" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A165" s="6" t="s">
         <v>30</v>
       </c>
@@ -16328,7 +16316,7 @@
       <c r="AD165" s="7"/>
       <c r="AE165" s="8"/>
     </row>
-    <row r="166" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A166" s="6" t="s">
         <v>30</v>
       </c>
@@ -16401,7 +16389,7 @@
       <c r="AD166" s="7"/>
       <c r="AE166" s="8"/>
     </row>
-    <row r="167" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A167" s="6" t="s">
         <v>30</v>
       </c>
@@ -16474,7 +16462,7 @@
       <c r="AD167" s="7"/>
       <c r="AE167" s="8"/>
     </row>
-    <row r="168" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A168" s="6" t="s">
         <v>30</v>
       </c>
@@ -16545,7 +16533,7 @@
       <c r="AD168" s="7"/>
       <c r="AE168" s="8"/>
     </row>
-    <row r="169" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A169" s="6" t="s">
         <v>30</v>
       </c>
@@ -16614,7 +16602,7 @@
       <c r="AD169" s="7"/>
       <c r="AE169" s="8"/>
     </row>
-    <row r="170" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A170" s="6" t="s">
         <v>30</v>
       </c>
@@ -16687,7 +16675,7 @@
       <c r="AD170" s="7"/>
       <c r="AE170" s="8"/>
     </row>
-    <row r="171" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A171" s="6" t="s">
         <v>30</v>
       </c>
@@ -16760,7 +16748,7 @@
       <c r="AD171" s="7"/>
       <c r="AE171" s="8"/>
     </row>
-    <row r="172" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A172" s="6" t="s">
         <v>30</v>
       </c>
@@ -16833,7 +16821,7 @@
       <c r="AD172" s="7"/>
       <c r="AE172" s="8"/>
     </row>
-    <row r="173" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A173" s="6" t="s">
         <v>30</v>
       </c>
@@ -16906,7 +16894,7 @@
       <c r="AD173" s="7"/>
       <c r="AE173" s="8"/>
     </row>
-    <row r="174" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A174" s="6" t="s">
         <v>30</v>
       </c>
@@ -16979,7 +16967,7 @@
       <c r="AD174" s="7"/>
       <c r="AE174" s="8"/>
     </row>
-    <row r="175" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A175" s="6" t="s">
         <v>30</v>
       </c>
@@ -17052,7 +17040,7 @@
       <c r="AD175" s="7"/>
       <c r="AE175" s="8"/>
     </row>
-    <row r="176" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A176" s="6" t="s">
         <v>30</v>
       </c>
@@ -17125,7 +17113,7 @@
       <c r="AD176" s="7"/>
       <c r="AE176" s="8"/>
     </row>
-    <row r="177" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A177" s="6" t="s">
         <v>30</v>
       </c>
@@ -17198,7 +17186,7 @@
       <c r="AD177" s="7"/>
       <c r="AE177" s="8"/>
     </row>
-    <row r="178" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A178" s="6" t="s">
         <v>30</v>
       </c>
@@ -17271,7 +17259,7 @@
       <c r="AD178" s="7"/>
       <c r="AE178" s="8"/>
     </row>
-    <row r="179" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A179" s="6" t="s">
         <v>30</v>
       </c>
@@ -17344,7 +17332,7 @@
       <c r="AD179" s="7"/>
       <c r="AE179" s="8"/>
     </row>
-    <row r="180" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A180" s="6" t="s">
         <v>30</v>
       </c>
@@ -17419,7 +17407,7 @@
       <c r="AD180" s="7"/>
       <c r="AE180" s="8"/>
     </row>
-    <row r="181" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A181" s="6" t="s">
         <v>30</v>
       </c>
@@ -17488,7 +17476,7 @@
       <c r="AD181" s="7"/>
       <c r="AE181" s="8"/>
     </row>
-    <row r="182" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A182" s="6" t="s">
         <v>30</v>
       </c>
@@ -17561,7 +17549,7 @@
       <c r="AD182" s="7"/>
       <c r="AE182" s="8"/>
     </row>
-    <row r="183" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A183" s="6" t="s">
         <v>30</v>
       </c>
@@ -17638,7 +17626,7 @@
       <c r="AD183" s="7"/>
       <c r="AE183" s="8"/>
     </row>
-    <row r="184" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A184" s="6" t="s">
         <v>30</v>
       </c>
@@ -17711,7 +17699,7 @@
       <c r="AD184" s="7"/>
       <c r="AE184" s="8"/>
     </row>
-    <row r="185" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A185" s="6" t="s">
         <v>30</v>
       </c>
@@ -17784,7 +17772,7 @@
       <c r="AD185" s="7"/>
       <c r="AE185" s="8"/>
     </row>
-    <row r="186" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A186" s="6" t="s">
         <v>30</v>
       </c>
@@ -17853,7 +17841,7 @@
       <c r="AD186" s="7"/>
       <c r="AE186" s="8"/>
     </row>
-    <row r="187" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A187" s="6" t="s">
         <v>117</v>
       </c>
@@ -17924,7 +17912,7 @@
       <c r="AD187" s="7"/>
       <c r="AE187" s="8"/>
     </row>
-    <row r="188" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A188" s="6" t="s">
         <v>117</v>
       </c>
@@ -17995,7 +17983,7 @@
       <c r="AD188" s="7"/>
       <c r="AE188" s="8"/>
     </row>
-    <row r="189" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A189" s="6" t="s">
         <v>117</v>
       </c>
@@ -18066,7 +18054,7 @@
       <c r="AD189" s="7"/>
       <c r="AE189" s="8"/>
     </row>
-    <row r="190" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A190" s="6" t="s">
         <v>117</v>
       </c>
@@ -18135,7 +18123,7 @@
       <c r="AD190" s="7"/>
       <c r="AE190" s="8"/>
     </row>
-    <row r="191" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A191" s="6" t="s">
         <v>30</v>
       </c>
@@ -18208,7 +18196,7 @@
       <c r="AD191" s="7"/>
       <c r="AE191" s="8"/>
     </row>
-    <row r="192" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A192" s="6" t="s">
         <v>30</v>
       </c>
@@ -18281,7 +18269,7 @@
       <c r="AD192" s="7"/>
       <c r="AE192" s="8"/>
     </row>
-    <row r="193" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A193" s="6" t="s">
         <v>30</v>
       </c>
@@ -18354,7 +18342,7 @@
       <c r="AD193" s="7"/>
       <c r="AE193" s="8"/>
     </row>
-    <row r="194" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A194" s="6" t="s">
         <v>30</v>
       </c>
@@ -18427,7 +18415,7 @@
       <c r="AD194" s="7"/>
       <c r="AE194" s="8"/>
     </row>
-    <row r="195" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A195" s="6" t="s">
         <v>30</v>
       </c>
@@ -18500,7 +18488,7 @@
       <c r="AD195" s="7"/>
       <c r="AE195" s="8"/>
     </row>
-    <row r="196" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A196" s="6" t="s">
         <v>30</v>
       </c>
@@ -18573,7 +18561,7 @@
       <c r="AD196" s="7"/>
       <c r="AE196" s="8"/>
     </row>
-    <row r="197" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A197" s="6" t="s">
         <v>30</v>
       </c>
@@ -18646,7 +18634,7 @@
       <c r="AD197" s="7"/>
       <c r="AE197" s="8"/>
     </row>
-    <row r="198" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A198" s="6" t="s">
         <v>30</v>
       </c>
@@ -18715,7 +18703,7 @@
       <c r="AD198" s="7"/>
       <c r="AE198" s="8"/>
     </row>
-    <row r="199" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A199" s="6" t="s">
         <v>30</v>
       </c>
@@ -18782,7 +18770,7 @@
       <c r="AD199" s="7"/>
       <c r="AE199" s="8"/>
     </row>
-    <row r="200" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A200" s="6" t="s">
         <v>30</v>
       </c>
@@ -18857,7 +18845,7 @@
       <c r="AD200" s="7"/>
       <c r="AE200" s="8"/>
     </row>
-    <row r="201" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A201" s="6" t="s">
         <v>30</v>
       </c>
@@ -18932,7 +18920,7 @@
       <c r="AD201" s="7"/>
       <c r="AE201" s="8"/>
     </row>
-    <row r="202" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A202" s="6" t="s">
         <v>30</v>
       </c>
@@ -19007,7 +18995,7 @@
       <c r="AD202" s="7"/>
       <c r="AE202" s="8"/>
     </row>
-    <row r="203" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A203" s="6" t="s">
         <v>30</v>
       </c>
@@ -19082,7 +19070,7 @@
       <c r="AD203" s="7"/>
       <c r="AE203" s="8"/>
     </row>
-    <row r="204" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A204" s="6" t="s">
         <v>30</v>
       </c>
@@ -19157,7 +19145,7 @@
       <c r="AD204" s="7"/>
       <c r="AE204" s="8"/>
     </row>
-    <row r="205" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A205" s="6" t="s">
         <v>30</v>
       </c>
@@ -19230,7 +19218,7 @@
       <c r="AD205" s="7"/>
       <c r="AE205" s="8"/>
     </row>
-    <row r="206" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A206" s="6" t="s">
         <v>30</v>
       </c>
@@ -19303,7 +19291,7 @@
       <c r="AD206" s="7"/>
       <c r="AE206" s="8"/>
     </row>
-    <row r="207" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A207" s="6" t="s">
         <v>30</v>
       </c>
@@ -19378,7 +19366,7 @@
       <c r="AD207" s="7"/>
       <c r="AE207" s="8"/>
     </row>
-    <row r="208" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A208" s="6" t="s">
         <v>30</v>
       </c>
@@ -19455,7 +19443,7 @@
       <c r="AD208" s="7"/>
       <c r="AE208" s="8"/>
     </row>
-    <row r="209" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A209" s="6" t="s">
         <v>30</v>
       </c>
@@ -19534,7 +19522,7 @@
       <c r="AD209" s="7"/>
       <c r="AE209" s="8"/>
     </row>
-    <row r="210" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A210" s="6" t="s">
         <v>30</v>
       </c>
@@ -19611,7 +19599,7 @@
       <c r="AD210" s="7"/>
       <c r="AE210" s="8"/>
     </row>
-    <row r="211" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A211" s="6" t="s">
         <v>30</v>
       </c>
@@ -19684,7 +19672,7 @@
       <c r="AD211" s="7"/>
       <c r="AE211" s="8"/>
     </row>
-    <row r="212" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A212" s="6" t="s">
         <v>30</v>
       </c>
@@ -19757,7 +19745,7 @@
       <c r="AD212" s="7"/>
       <c r="AE212" s="8"/>
     </row>
-    <row r="213" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A213" s="6" t="s">
         <v>30</v>
       </c>
@@ -19830,7 +19818,7 @@
       <c r="AD213" s="7"/>
       <c r="AE213" s="8"/>
     </row>
-    <row r="214" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A214" s="6" t="s">
         <v>30</v>
       </c>
@@ -19903,7 +19891,7 @@
       <c r="AD214" s="7"/>
       <c r="AE214" s="8"/>
     </row>
-    <row r="215" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A215" s="6" t="s">
         <v>30</v>
       </c>
@@ -19976,7 +19964,7 @@
       <c r="AD215" s="7"/>
       <c r="AE215" s="8"/>
     </row>
-    <row r="216" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A216" s="6" t="s">
         <v>30</v>
       </c>
@@ -20057,7 +20045,7 @@
       <c r="AD216" s="7"/>
       <c r="AE216" s="8"/>
     </row>
-    <row r="217" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A217" s="6" t="s">
         <v>30</v>
       </c>
@@ -20140,7 +20128,7 @@
       <c r="AD217" s="7"/>
       <c r="AE217" s="8"/>
     </row>
-    <row r="218" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A218" s="6" t="s">
         <v>30</v>
       </c>
@@ -20221,7 +20209,7 @@
       <c r="AD218" s="7"/>
       <c r="AE218" s="8"/>
     </row>
-    <row r="219" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A219" s="6" t="s">
         <v>30</v>
       </c>
@@ -20302,7 +20290,7 @@
       <c r="AD219" s="7"/>
       <c r="AE219" s="8"/>
     </row>
-    <row r="220" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A220" s="6" t="s">
         <v>30</v>
       </c>
@@ -20381,7 +20369,7 @@
       <c r="AD220" s="7"/>
       <c r="AE220" s="8"/>
     </row>
-    <row r="221" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A221" s="6" t="s">
         <v>30</v>
       </c>
@@ -20460,7 +20448,7 @@
       <c r="AD221" s="7"/>
       <c r="AE221" s="8"/>
     </row>
-    <row r="222" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A222" s="6" t="s">
         <v>30</v>
       </c>
@@ -20539,7 +20527,7 @@
       <c r="AD222" s="7"/>
       <c r="AE222" s="8"/>
     </row>
-    <row r="223" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A223" s="6" t="s">
         <v>30</v>
       </c>
@@ -20618,7 +20606,7 @@
       <c r="AD223" s="7"/>
       <c r="AE223" s="8"/>
     </row>
-    <row r="224" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A224" s="6" t="s">
         <v>30</v>
       </c>
@@ -20693,7 +20681,7 @@
       <c r="AD224" s="7"/>
       <c r="AE224" s="8"/>
     </row>
-    <row r="225" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A225" s="6" t="s">
         <v>30</v>
       </c>
@@ -20766,7 +20754,7 @@
       <c r="AD225" s="7"/>
       <c r="AE225" s="8"/>
     </row>
-    <row r="226" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A226" s="6" t="s">
         <v>30</v>
       </c>
@@ -20839,7 +20827,7 @@
       <c r="AD226" s="7"/>
       <c r="AE226" s="8"/>
     </row>
-    <row r="227" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A227" s="6" t="s">
         <v>30</v>
       </c>
@@ -20912,7 +20900,7 @@
       <c r="AD227" s="7"/>
       <c r="AE227" s="8"/>
     </row>
-    <row r="228" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A228" s="6" t="s">
         <v>30</v>
       </c>
@@ -20985,7 +20973,7 @@
       <c r="AD228" s="7"/>
       <c r="AE228" s="8"/>
     </row>
-    <row r="229" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A229" s="6" t="s">
         <v>30</v>
       </c>
@@ -21058,7 +21046,7 @@
       <c r="AD229" s="7"/>
       <c r="AE229" s="8"/>
     </row>
-    <row r="230" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A230" s="6" t="s">
         <v>30</v>
       </c>
@@ -21131,7 +21119,7 @@
       <c r="AD230" s="7"/>
       <c r="AE230" s="8"/>
     </row>
-    <row r="231" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A231" s="6" t="s">
         <v>30</v>
       </c>
@@ -21204,7 +21192,7 @@
       <c r="AD231" s="7"/>
       <c r="AE231" s="8"/>
     </row>
-    <row r="232" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A232" s="6" t="s">
         <v>30</v>
       </c>
@@ -21277,7 +21265,7 @@
       <c r="AD232" s="7"/>
       <c r="AE232" s="8"/>
     </row>
-    <row r="233" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A233" s="6" t="s">
         <v>30</v>
       </c>
@@ -21350,7 +21338,7 @@
       <c r="AD233" s="7"/>
       <c r="AE233" s="8"/>
     </row>
-    <row r="234" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A234" s="6" t="s">
         <v>30</v>
       </c>
@@ -21423,7 +21411,7 @@
       <c r="AD234" s="7"/>
       <c r="AE234" s="8"/>
     </row>
-    <row r="235" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A235" s="6" t="s">
         <v>30</v>
       </c>
@@ -21496,7 +21484,7 @@
       <c r="AD235" s="7"/>
       <c r="AE235" s="8"/>
     </row>
-    <row r="236" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A236" s="6" t="s">
         <v>30</v>
       </c>
@@ -21569,7 +21557,7 @@
       <c r="AD236" s="7"/>
       <c r="AE236" s="8"/>
     </row>
-    <row r="237" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A237" s="6" t="s">
         <v>30</v>
       </c>
@@ -21642,7 +21630,7 @@
       <c r="AD237" s="7"/>
       <c r="AE237" s="8"/>
     </row>
-    <row r="238" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A238" s="6" t="s">
         <v>30</v>
       </c>
@@ -21715,7 +21703,7 @@
       <c r="AD238" s="7"/>
       <c r="AE238" s="8"/>
     </row>
-    <row r="239" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A239" s="6" t="s">
         <v>30</v>
       </c>
@@ -21788,7 +21776,7 @@
       <c r="AD239" s="7"/>
       <c r="AE239" s="8"/>
     </row>
-    <row r="240" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A240" s="6" t="s">
         <v>30</v>
       </c>
@@ -21861,7 +21849,7 @@
       <c r="AD240" s="7"/>
       <c r="AE240" s="8"/>
     </row>
-    <row r="241" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A241" s="6" t="s">
         <v>30</v>
       </c>
@@ -21934,7 +21922,7 @@
       <c r="AD241" s="7"/>
       <c r="AE241" s="8"/>
     </row>
-    <row r="242" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A242" s="6" t="s">
         <v>30</v>
       </c>
@@ -22007,7 +21995,7 @@
       <c r="AD242" s="7"/>
       <c r="AE242" s="8"/>
     </row>
-    <row r="243" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A243" s="6" t="s">
         <v>30</v>
       </c>
@@ -22080,7 +22068,7 @@
       <c r="AD243" s="7"/>
       <c r="AE243" s="8"/>
     </row>
-    <row r="244" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A244" s="6" t="s">
         <v>30</v>
       </c>
@@ -22153,7 +22141,7 @@
       <c r="AD244" s="7"/>
       <c r="AE244" s="8"/>
     </row>
-    <row r="245" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A245" s="6" t="s">
         <v>30</v>
       </c>
@@ -22226,7 +22214,7 @@
       <c r="AD245" s="7"/>
       <c r="AE245" s="8"/>
     </row>
-    <row r="246" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A246" s="6" t="s">
         <v>30</v>
       </c>
@@ -22299,7 +22287,7 @@
       <c r="AD246" s="7"/>
       <c r="AE246" s="8"/>
     </row>
-    <row r="247" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A247" s="6" t="s">
         <v>30</v>
       </c>
@@ -22372,7 +22360,7 @@
       <c r="AD247" s="7"/>
       <c r="AE247" s="8"/>
     </row>
-    <row r="248" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A248" s="6" t="s">
         <v>30</v>
       </c>
@@ -22445,7 +22433,7 @@
       <c r="AD248" s="7"/>
       <c r="AE248" s="8"/>
     </row>
-    <row r="249" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A249" s="6" t="s">
         <v>30</v>
       </c>
@@ -22518,7 +22506,7 @@
       <c r="AD249" s="7"/>
       <c r="AE249" s="8"/>
     </row>
-    <row r="250" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A250" s="6" t="s">
         <v>30</v>
       </c>
@@ -22591,7 +22579,7 @@
       <c r="AD250" s="7"/>
       <c r="AE250" s="8"/>
     </row>
-    <row r="251" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A251" s="6" t="s">
         <v>30</v>
       </c>
@@ -22664,7 +22652,7 @@
       <c r="AD251" s="7"/>
       <c r="AE251" s="8"/>
     </row>
-    <row r="252" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A252" s="6" t="s">
         <v>30</v>
       </c>
@@ -22737,7 +22725,7 @@
       <c r="AD252" s="7"/>
       <c r="AE252" s="8"/>
     </row>
-    <row r="253" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A253" s="6" t="s">
         <v>30</v>
       </c>
@@ -22810,7 +22798,7 @@
       <c r="AD253" s="7"/>
       <c r="AE253" s="8"/>
     </row>
-    <row r="254" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A254" s="6" t="s">
         <v>30</v>
       </c>
@@ -22883,7 +22871,7 @@
       <c r="AD254" s="7"/>
       <c r="AE254" s="8"/>
     </row>
-    <row r="255" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A255" s="6" t="s">
         <v>30</v>
       </c>
@@ -22956,7 +22944,7 @@
       <c r="AD255" s="7"/>
       <c r="AE255" s="8"/>
     </row>
-    <row r="256" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A256" s="6" t="s">
         <v>30</v>
       </c>
@@ -23029,7 +23017,7 @@
       <c r="AD256" s="7"/>
       <c r="AE256" s="8"/>
     </row>
-    <row r="257" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A257" s="6" t="s">
         <v>30</v>
       </c>
@@ -23102,7 +23090,7 @@
       <c r="AD257" s="7"/>
       <c r="AE257" s="8"/>
     </row>
-    <row r="258" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A258" s="6" t="s">
         <v>30</v>
       </c>
@@ -23175,7 +23163,7 @@
       <c r="AD258" s="7"/>
       <c r="AE258" s="8"/>
     </row>
-    <row r="259" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A259" s="6" t="s">
         <v>30</v>
       </c>
@@ -23248,7 +23236,7 @@
       <c r="AD259" s="7"/>
       <c r="AE259" s="8"/>
     </row>
-    <row r="260" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A260" s="6" t="s">
         <v>30</v>
       </c>
@@ -23321,7 +23309,7 @@
       <c r="AD260" s="7"/>
       <c r="AE260" s="8"/>
     </row>
-    <row r="261" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A261" s="6" t="s">
         <v>30</v>
       </c>
@@ -23394,7 +23382,7 @@
       <c r="AD261" s="7"/>
       <c r="AE261" s="8"/>
     </row>
-    <row r="262" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A262" s="6" t="s">
         <v>30</v>
       </c>
@@ -23467,7 +23455,7 @@
       <c r="AD262" s="7"/>
       <c r="AE262" s="8"/>
     </row>
-    <row r="263" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A263" s="6" t="s">
         <v>30</v>
       </c>
@@ -23540,7 +23528,7 @@
       <c r="AD263" s="7"/>
       <c r="AE263" s="8"/>
     </row>
-    <row r="264" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A264" s="6" t="s">
         <v>30</v>
       </c>
@@ -23613,7 +23601,7 @@
       <c r="AD264" s="7"/>
       <c r="AE264" s="8"/>
     </row>
-    <row r="265" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A265" s="6" t="s">
         <v>30</v>
       </c>
@@ -23686,7 +23674,7 @@
       <c r="AD265" s="7"/>
       <c r="AE265" s="8"/>
     </row>
-    <row r="266" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A266" s="6" t="s">
         <v>30</v>
       </c>
@@ -23759,7 +23747,7 @@
       <c r="AD266" s="7"/>
       <c r="AE266" s="8"/>
     </row>
-    <row r="267" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A267" s="6" t="s">
         <v>30</v>
       </c>
@@ -23832,7 +23820,7 @@
       <c r="AD267" s="7"/>
       <c r="AE267" s="8"/>
     </row>
-    <row r="268" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A268" s="6" t="s">
         <v>30</v>
       </c>
@@ -23905,7 +23893,7 @@
       <c r="AD268" s="7"/>
       <c r="AE268" s="8"/>
     </row>
-    <row r="269" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A269" s="6" t="s">
         <v>30</v>
       </c>
@@ -23978,7 +23966,7 @@
       <c r="AD269" s="7"/>
       <c r="AE269" s="8"/>
     </row>
-    <row r="270" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A270" s="6" t="s">
         <v>30</v>
       </c>
@@ -24051,7 +24039,7 @@
       <c r="AD270" s="7"/>
       <c r="AE270" s="8"/>
     </row>
-    <row r="271" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A271" s="6" t="s">
         <v>30</v>
       </c>
@@ -24124,7 +24112,7 @@
       <c r="AD271" s="7"/>
       <c r="AE271" s="8"/>
     </row>
-    <row r="272" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A272" s="6" t="s">
         <v>30</v>
       </c>
@@ -24197,7 +24185,7 @@
       <c r="AD272" s="7"/>
       <c r="AE272" s="8"/>
     </row>
-    <row r="273" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A273" s="6" t="s">
         <v>30</v>
       </c>
@@ -24270,7 +24258,7 @@
       <c r="AD273" s="7"/>
       <c r="AE273" s="8"/>
     </row>
-    <row r="274" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A274" s="6" t="s">
         <v>30</v>
       </c>
@@ -24343,7 +24331,7 @@
       <c r="AD274" s="7"/>
       <c r="AE274" s="8"/>
     </row>
-    <row r="275" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A275" s="6" t="s">
         <v>30</v>
       </c>
@@ -24416,7 +24404,7 @@
       <c r="AD275" s="7"/>
       <c r="AE275" s="8"/>
     </row>
-    <row r="276" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A276" s="6" t="s">
         <v>30</v>
       </c>
@@ -24489,7 +24477,7 @@
       <c r="AD276" s="7"/>
       <c r="AE276" s="8"/>
     </row>
-    <row r="277" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A277" s="6" t="s">
         <v>30</v>
       </c>
@@ -24562,7 +24550,7 @@
       <c r="AD277" s="7"/>
       <c r="AE277" s="8"/>
     </row>
-    <row r="278" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A278" s="6" t="s">
         <v>30</v>
       </c>
@@ -24635,7 +24623,7 @@
       <c r="AD278" s="7"/>
       <c r="AE278" s="8"/>
     </row>
-    <row r="279" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A279" s="6" t="s">
         <v>30</v>
       </c>
@@ -24708,7 +24696,7 @@
       <c r="AD279" s="7"/>
       <c r="AE279" s="8"/>
     </row>
-    <row r="280" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A280" s="6" t="s">
         <v>30</v>
       </c>
@@ -24781,7 +24769,7 @@
       <c r="AD280" s="7"/>
       <c r="AE280" s="8"/>
     </row>
-    <row r="281" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A281" s="6" t="s">
         <v>30</v>
       </c>
@@ -24854,7 +24842,7 @@
       <c r="AD281" s="7"/>
       <c r="AE281" s="8"/>
     </row>
-    <row r="282" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A282" s="6" t="s">
         <v>30</v>
       </c>
@@ -24927,7 +24915,7 @@
       <c r="AD282" s="7"/>
       <c r="AE282" s="8"/>
     </row>
-    <row r="283" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A283" s="6" t="s">
         <v>30</v>
       </c>
@@ -25000,7 +24988,7 @@
       <c r="AD283" s="7"/>
       <c r="AE283" s="8"/>
     </row>
-    <row r="284" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A284" s="6" t="s">
         <v>30</v>
       </c>
@@ -25073,7 +25061,7 @@
       <c r="AD284" s="7"/>
       <c r="AE284" s="8"/>
     </row>
-    <row r="285" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A285" s="6" t="s">
         <v>30</v>
       </c>
@@ -25146,7 +25134,7 @@
       <c r="AD285" s="7"/>
       <c r="AE285" s="8"/>
     </row>
-    <row r="286" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A286" s="6" t="s">
         <v>30</v>
       </c>
@@ -25219,7 +25207,7 @@
       <c r="AD286" s="7"/>
       <c r="AE286" s="8"/>
     </row>
-    <row r="287" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A287" s="6" t="s">
         <v>30</v>
       </c>
@@ -25292,7 +25280,7 @@
       <c r="AD287" s="7"/>
       <c r="AE287" s="8"/>
     </row>
-    <row r="288" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A288" s="6" t="s">
         <v>30</v>
       </c>
@@ -25365,7 +25353,7 @@
       <c r="AD288" s="7"/>
       <c r="AE288" s="8"/>
     </row>
-    <row r="289" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A289" s="6" t="s">
         <v>30</v>
       </c>
@@ -25438,7 +25426,7 @@
       <c r="AD289" s="7"/>
       <c r="AE289" s="8"/>
     </row>
-    <row r="290" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A290" s="6" t="s">
         <v>30</v>
       </c>
@@ -25511,7 +25499,7 @@
       <c r="AD290" s="7"/>
       <c r="AE290" s="8"/>
     </row>
-    <row r="291" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A291" s="6" t="s">
         <v>30</v>
       </c>
@@ -25584,7 +25572,7 @@
       <c r="AD291" s="7"/>
       <c r="AE291" s="8"/>
     </row>
-    <row r="292" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A292" s="6" t="s">
         <v>30</v>
       </c>
@@ -25657,7 +25645,7 @@
       <c r="AD292" s="7"/>
       <c r="AE292" s="8"/>
     </row>
-    <row r="293" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A293" s="6" t="s">
         <v>30</v>
       </c>
@@ -25730,7 +25718,7 @@
       <c r="AD293" s="7"/>
       <c r="AE293" s="8"/>
     </row>
-    <row r="294" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A294" s="6" t="s">
         <v>30</v>
       </c>
@@ -25803,7 +25791,7 @@
       <c r="AD294" s="7"/>
       <c r="AE294" s="8"/>
     </row>
-    <row r="295" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A295" s="6" t="s">
         <v>30</v>
       </c>
@@ -25876,7 +25864,7 @@
       <c r="AD295" s="7"/>
       <c r="AE295" s="8"/>
     </row>
-    <row r="296" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A296" s="6" t="s">
         <v>30</v>
       </c>
@@ -25949,7 +25937,7 @@
       <c r="AD296" s="7"/>
       <c r="AE296" s="8"/>
     </row>
-    <row r="297" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A297" s="6" t="s">
         <v>30</v>
       </c>
@@ -26022,7 +26010,7 @@
       <c r="AD297" s="7"/>
       <c r="AE297" s="8"/>
     </row>
-    <row r="298" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A298" s="6" t="s">
         <v>30</v>
       </c>
@@ -26095,7 +26083,7 @@
       <c r="AD298" s="7"/>
       <c r="AE298" s="8"/>
     </row>
-    <row r="299" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A299" s="6" t="s">
         <v>30</v>
       </c>
@@ -26168,7 +26156,7 @@
       <c r="AD299" s="7"/>
       <c r="AE299" s="8"/>
     </row>
-    <row r="300" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A300" s="6" t="s">
         <v>30</v>
       </c>
@@ -26241,7 +26229,7 @@
       <c r="AD300" s="7"/>
       <c r="AE300" s="8"/>
     </row>
-    <row r="301" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A301" s="6" t="s">
         <v>30</v>
       </c>
@@ -26314,7 +26302,7 @@
       <c r="AD301" s="7"/>
       <c r="AE301" s="8"/>
     </row>
-    <row r="302" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A302" s="6" t="s">
         <v>30</v>
       </c>
@@ -26387,7 +26375,7 @@
       <c r="AD302" s="7"/>
       <c r="AE302" s="8"/>
     </row>
-    <row r="303" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A303" s="6" t="s">
         <v>30</v>
       </c>
@@ -26466,7 +26454,7 @@
       <c r="AD303" s="7"/>
       <c r="AE303" s="8"/>
     </row>
-    <row r="304" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A304" s="6" t="s">
         <v>30</v>
       </c>
@@ -26545,7 +26533,7 @@
       <c r="AD304" s="7"/>
       <c r="AE304" s="8"/>
     </row>
-    <row r="305" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A305" s="6" t="s">
         <v>30</v>
       </c>
@@ -26620,7 +26608,7 @@
       <c r="AD305" s="7"/>
       <c r="AE305" s="8"/>
     </row>
-    <row r="306" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A306" s="6" t="s">
         <v>30</v>
       </c>
@@ -26695,7 +26683,7 @@
       <c r="AD306" s="7"/>
       <c r="AE306" s="8"/>
     </row>
-    <row r="307" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A307" s="6" t="s">
         <v>30</v>
       </c>
@@ -26770,7 +26758,7 @@
       <c r="AD307" s="7"/>
       <c r="AE307" s="8"/>
     </row>
-    <row r="308" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A308" s="6" t="s">
         <v>30</v>
       </c>
@@ -26845,7 +26833,7 @@
       <c r="AD308" s="7"/>
       <c r="AE308" s="8"/>
     </row>
-    <row r="309" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A309" s="6" t="s">
         <v>30</v>
       </c>
@@ -26920,7 +26908,7 @@
       <c r="AD309" s="7"/>
       <c r="AE309" s="8"/>
     </row>
-    <row r="310" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A310" s="6" t="s">
         <v>30</v>
       </c>
@@ -26995,7 +26983,7 @@
       <c r="AD310" s="7"/>
       <c r="AE310" s="8"/>
     </row>
-    <row r="311" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A311" s="6" t="s">
         <v>30</v>
       </c>
@@ -27070,7 +27058,7 @@
       <c r="AD311" s="7"/>
       <c r="AE311" s="8"/>
     </row>
-    <row r="312" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A312" s="6" t="s">
         <v>30</v>
       </c>
@@ -27147,7 +27135,7 @@
       <c r="AD312" s="7"/>
       <c r="AE312" s="8"/>
     </row>
-    <row r="313" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A313" s="6" t="s">
         <v>30</v>
       </c>
@@ -27220,7 +27208,7 @@
       <c r="AD313" s="7"/>
       <c r="AE313" s="8"/>
     </row>
-    <row r="314" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A314" s="6" t="s">
         <v>30</v>
       </c>
@@ -27293,7 +27281,7 @@
       <c r="AD314" s="7"/>
       <c r="AE314" s="8"/>
     </row>
-    <row r="315" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A315" s="6" t="s">
         <v>30</v>
       </c>
@@ -27370,7 +27358,7 @@
       <c r="AD315" s="7"/>
       <c r="AE315" s="8"/>
     </row>
-    <row r="316" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A316" s="6" t="s">
         <v>30</v>
       </c>
@@ -27437,7 +27425,7 @@
       <c r="AD316" s="7"/>
       <c r="AE316" s="8"/>
     </row>
-    <row r="317" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A317" s="6" t="s">
         <v>30</v>
       </c>
@@ -27508,7 +27496,7 @@
       <c r="AD317" s="7"/>
       <c r="AE317" s="8"/>
     </row>
-    <row r="318" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A318" s="6" t="s">
         <v>30</v>
       </c>
@@ -27575,7 +27563,7 @@
       <c r="AD318" s="7"/>
       <c r="AE318" s="8"/>
     </row>
-    <row r="319" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A319" s="6" t="s">
         <v>30</v>
       </c>
@@ -27644,7 +27632,7 @@
       <c r="AD319" s="7"/>
       <c r="AE319" s="8"/>
     </row>
-    <row r="320" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A320" s="6" t="s">
         <v>30</v>
       </c>
@@ -27713,7 +27701,7 @@
       <c r="AD320" s="7"/>
       <c r="AE320" s="8"/>
     </row>
-    <row r="321" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A321" s="6" t="s">
         <v>30</v>
       </c>
@@ -27782,7 +27770,7 @@
       <c r="AD321" s="7"/>
       <c r="AE321" s="8"/>
     </row>
-    <row r="322" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A322" s="6" t="s">
         <v>30</v>
       </c>
@@ -27855,7 +27843,7 @@
       <c r="AD322" s="7"/>
       <c r="AE322" s="8"/>
     </row>
-    <row r="323" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A323" s="6" t="s">
         <v>30</v>
       </c>
@@ -27928,7 +27916,7 @@
       <c r="AD323" s="7"/>
       <c r="AE323" s="8"/>
     </row>
-    <row r="324" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A324" s="6" t="s">
         <v>30</v>
       </c>
@@ -28001,7 +27989,7 @@
       <c r="AD324" s="7"/>
       <c r="AE324" s="8"/>
     </row>
-    <row r="325" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A325" s="6" t="s">
         <v>30</v>
       </c>
@@ -28074,7 +28062,7 @@
       <c r="AD325" s="7"/>
       <c r="AE325" s="8"/>
     </row>
-    <row r="326" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A326" s="6" t="s">
         <v>30</v>
       </c>
@@ -28147,7 +28135,7 @@
       <c r="AD326" s="7"/>
       <c r="AE326" s="8"/>
     </row>
-    <row r="327" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A327" s="6" t="s">
         <v>30</v>
       </c>
@@ -28214,7 +28202,7 @@
       <c r="AD327" s="7"/>
       <c r="AE327" s="8"/>
     </row>
-    <row r="328" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A328" s="6" t="s">
         <v>30</v>
       </c>
@@ -28291,7 +28279,7 @@
       <c r="AD328" s="7"/>
       <c r="AE328" s="8"/>
     </row>
-    <row r="329" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A329" s="6" t="s">
         <v>30</v>
       </c>
@@ -28364,7 +28352,7 @@
       <c r="AD329" s="7"/>
       <c r="AE329" s="8"/>
     </row>
-    <row r="330" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A330" s="6" t="s">
         <v>117</v>
       </c>
@@ -28437,7 +28425,7 @@
       <c r="AD330" s="7"/>
       <c r="AE330" s="8"/>
     </row>
-    <row r="331" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A331" s="6" t="s">
         <v>117</v>
       </c>
@@ -28510,7 +28498,7 @@
       <c r="AD331" s="7"/>
       <c r="AE331" s="8"/>
     </row>
-    <row r="332" spans="1:31" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:31" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A332" s="6" t="s">
         <v>117</v>
       </c>
@@ -28573,17 +28561,17 @@
         <v>41</v>
       </c>
       <c r="AB332" s="6"/>
-      <c r="AC332" s="7" t="s">
-        <v>1223</v>
+      <c r="AC332" s="7">
+        <v>0</v>
       </c>
       <c r="AD332" s="7" t="s">
         <v>1216</v>
       </c>
       <c r="AE332" s="8" t="s">
-        <v>1224</v>
-      </c>
-    </row>
-    <row r="333" spans="1:31" ht="43.5" x14ac:dyDescent="0.35">
+        <v>1223</v>
+      </c>
+    </row>
+    <row r="333" spans="1:31" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A333" s="6" t="s">
         <v>117</v>
       </c>
@@ -28646,17 +28634,17 @@
         <v>41</v>
       </c>
       <c r="AB333" s="6"/>
-      <c r="AC333" s="7" t="s">
-        <v>1223</v>
+      <c r="AC333" s="7">
+        <v>0</v>
       </c>
       <c r="AD333" s="7" t="s">
         <v>1216</v>
       </c>
       <c r="AE333" s="8" t="s">
-        <v>1224</v>
-      </c>
-    </row>
-    <row r="334" spans="1:31" x14ac:dyDescent="0.35">
+        <v>1223</v>
+      </c>
+    </row>
+    <row r="334" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A334" s="6" t="s">
         <v>117</v>
       </c>
@@ -28727,7 +28715,7 @@
       <c r="AD334" s="7"/>
       <c r="AE334" s="8"/>
     </row>
-    <row r="335" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A335" s="6" t="s">
         <v>30</v>
       </c>
@@ -28808,7 +28796,7 @@
       <c r="AD335" s="7"/>
       <c r="AE335" s="8"/>
     </row>
-    <row r="336" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A336" s="6" t="s">
         <v>30</v>
       </c>
@@ -28887,7 +28875,7 @@
       <c r="AD336" s="7"/>
       <c r="AE336" s="8"/>
     </row>
-    <row r="337" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A337" s="6" t="s">
         <v>30</v>
       </c>
@@ -28960,7 +28948,7 @@
       <c r="AD337" s="7"/>
       <c r="AE337" s="8"/>
     </row>
-    <row r="338" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A338" s="6" t="s">
         <v>30</v>
       </c>
@@ -29033,7 +29021,7 @@
       <c r="AD338" s="7"/>
       <c r="AE338" s="8"/>
     </row>
-    <row r="339" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A339" s="6" t="s">
         <v>30</v>
       </c>
@@ -29106,7 +29094,7 @@
       <c r="AD339" s="7"/>
       <c r="AE339" s="8"/>
     </row>
-    <row r="340" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A340" s="6" t="s">
         <v>30</v>
       </c>
@@ -29179,7 +29167,7 @@
       <c r="AD340" s="7"/>
       <c r="AE340" s="8"/>
     </row>
-    <row r="341" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A341" s="6" t="s">
         <v>30</v>
       </c>
@@ -29252,7 +29240,7 @@
       <c r="AD341" s="7"/>
       <c r="AE341" s="8"/>
     </row>
-    <row r="342" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A342" s="6" t="s">
         <v>30</v>
       </c>
@@ -29325,7 +29313,7 @@
       <c r="AD342" s="7"/>
       <c r="AE342" s="8"/>
     </row>
-    <row r="343" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A343" s="6" t="s">
         <v>117</v>
       </c>
@@ -29394,7 +29382,7 @@
       <c r="AD343" s="7"/>
       <c r="AE343" s="8"/>
     </row>
-    <row r="344" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A344" s="6" t="s">
         <v>30</v>
       </c>
@@ -29467,7 +29455,7 @@
       <c r="AD344" s="7"/>
       <c r="AE344" s="8"/>
     </row>
-    <row r="345" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A345" s="6" t="s">
         <v>30</v>
       </c>
@@ -29540,7 +29528,7 @@
       <c r="AD345" s="7"/>
       <c r="AE345" s="8"/>
     </row>
-    <row r="346" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A346" s="6" t="s">
         <v>30</v>
       </c>
@@ -29613,7 +29601,7 @@
       <c r="AD346" s="7"/>
       <c r="AE346" s="8"/>
     </row>
-    <row r="347" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A347" s="6" t="s">
         <v>30</v>
       </c>
@@ -29686,7 +29674,7 @@
       <c r="AD347" s="7"/>
       <c r="AE347" s="8"/>
     </row>
-    <row r="348" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A348" s="6" t="s">
         <v>30</v>
       </c>
@@ -29759,7 +29747,7 @@
       <c r="AD348" s="7"/>
       <c r="AE348" s="8"/>
     </row>
-    <row r="349" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A349" s="6" t="s">
         <v>30</v>
       </c>
@@ -29832,7 +29820,7 @@
       <c r="AD349" s="7"/>
       <c r="AE349" s="8"/>
     </row>
-    <row r="350" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A350" s="6" t="s">
         <v>30</v>
       </c>
@@ -29909,7 +29897,7 @@
       <c r="AD350" s="7"/>
       <c r="AE350" s="8"/>
     </row>
-    <row r="351" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A351" s="6" t="s">
         <v>30</v>
       </c>
@@ -29986,7 +29974,7 @@
       <c r="AD351" s="7"/>
       <c r="AE351" s="8"/>
     </row>
-    <row r="352" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A352" s="6" t="s">
         <v>30</v>
       </c>
@@ -30063,7 +30051,7 @@
       <c r="AD352" s="7"/>
       <c r="AE352" s="8"/>
     </row>
-    <row r="353" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A353" s="6" t="s">
         <v>30</v>
       </c>
@@ -30130,7 +30118,7 @@
       <c r="AD353" s="7"/>
       <c r="AE353" s="8"/>
     </row>
-    <row r="354" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A354" s="6" t="s">
         <v>30</v>
       </c>
@@ -30205,7 +30193,7 @@
       <c r="AD354" s="7"/>
       <c r="AE354" s="8"/>
     </row>
-    <row r="355" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A355" s="6" t="s">
         <v>30</v>
       </c>
@@ -30276,7 +30264,7 @@
       <c r="AD355" s="7"/>
       <c r="AE355" s="8"/>
     </row>
-    <row r="356" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A356" s="6" t="s">
         <v>30</v>
       </c>
@@ -30351,7 +30339,7 @@
       <c r="AD356" s="7"/>
       <c r="AE356" s="8"/>
     </row>
-    <row r="357" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A357" s="6" t="s">
         <v>30</v>
       </c>
@@ -30426,7 +30414,7 @@
       <c r="AD357" s="7"/>
       <c r="AE357" s="8"/>
     </row>
-    <row r="358" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A358" s="6" t="s">
         <v>30</v>
       </c>
@@ -30501,7 +30489,7 @@
       <c r="AD358" s="7"/>
       <c r="AE358" s="8"/>
     </row>
-    <row r="359" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A359" s="6" t="s">
         <v>30</v>
       </c>
@@ -30576,7 +30564,7 @@
       <c r="AD359" s="7"/>
       <c r="AE359" s="8"/>
     </row>
-    <row r="360" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A360" s="6" t="s">
         <v>30</v>
       </c>
@@ -30645,7 +30633,7 @@
       <c r="AD360" s="7"/>
       <c r="AE360" s="8"/>
     </row>
-    <row r="361" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A361" s="6" t="s">
         <v>30</v>
       </c>
@@ -30722,7 +30710,7 @@
       <c r="AD361" s="7"/>
       <c r="AE361" s="8"/>
     </row>
-    <row r="362" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A362" s="6" t="s">
         <v>30</v>
       </c>
@@ -30799,7 +30787,7 @@
       <c r="AD362" s="7"/>
       <c r="AE362" s="8"/>
     </row>
-    <row r="363" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A363" s="6" t="s">
         <v>30</v>
       </c>
@@ -30880,7 +30868,7 @@
       <c r="AD363" s="7"/>
       <c r="AE363" s="8"/>
     </row>
-    <row r="364" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A364" s="6" t="s">
         <v>30</v>
       </c>
@@ -30965,7 +30953,7 @@
       <c r="AD364" s="7"/>
       <c r="AE364" s="8"/>
     </row>
-    <row r="365" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A365" s="6" t="s">
         <v>30</v>
       </c>
@@ -31048,7 +31036,7 @@
       <c r="AD365" s="7"/>
       <c r="AE365" s="8"/>
     </row>
-    <row r="366" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A366" s="6" t="s">
         <v>30</v>
       </c>
@@ -31125,7 +31113,7 @@
       <c r="AD366" s="7"/>
       <c r="AE366" s="8"/>
     </row>
-    <row r="367" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A367" s="6" t="s">
         <v>30</v>
       </c>
@@ -31202,7 +31190,7 @@
       <c r="AD367" s="7"/>
       <c r="AE367" s="8"/>
     </row>
-    <row r="368" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A368" s="6" t="s">
         <v>30</v>
       </c>
@@ -31279,7 +31267,7 @@
       <c r="AD368" s="7"/>
       <c r="AE368" s="8"/>
     </row>
-    <row r="369" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A369" s="6" t="s">
         <v>30</v>
       </c>
@@ -31356,7 +31344,7 @@
       <c r="AD369" s="7"/>
       <c r="AE369" s="8"/>
     </row>
-    <row r="370" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A370" s="6" t="s">
         <v>30</v>
       </c>
@@ -31433,7 +31421,7 @@
       <c r="AD370" s="7"/>
       <c r="AE370" s="8"/>
     </row>
-    <row r="371" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A371" s="6" t="s">
         <v>30</v>
       </c>
@@ -31510,7 +31498,7 @@
       <c r="AD371" s="7"/>
       <c r="AE371" s="8"/>
     </row>
-    <row r="372" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A372" s="6" t="s">
         <v>30</v>
       </c>
@@ -31587,7 +31575,7 @@
       <c r="AD372" s="7"/>
       <c r="AE372" s="8"/>
     </row>
-    <row r="373" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A373" s="6" t="s">
         <v>30</v>
       </c>
@@ -31661,12 +31649,12 @@
         <v>41</v>
       </c>
       <c r="AC373" s="7">
-        <v>27.5</v>
+        <v>2.0529999999999999</v>
       </c>
       <c r="AD373" s="7"/>
       <c r="AE373" s="8"/>
     </row>
-    <row r="374" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A374" s="6" t="s">
         <v>30</v>
       </c>
@@ -31739,7 +31727,7 @@
       <c r="AD374" s="7"/>
       <c r="AE374" s="8"/>
     </row>
-    <row r="375" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A375" s="6" t="s">
         <v>30</v>
       </c>
@@ -31810,7 +31798,7 @@
       <c r="AD375" s="7"/>
       <c r="AE375" s="8"/>
     </row>
-    <row r="376" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A376" s="6" t="s">
         <v>30</v>
       </c>
@@ -31881,7 +31869,7 @@
       <c r="AD376" s="7"/>
       <c r="AE376" s="8"/>
     </row>
-    <row r="377" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A377" s="6" t="s">
         <v>30</v>
       </c>
@@ -31954,7 +31942,7 @@
       <c r="AD377" s="7"/>
       <c r="AE377" s="8"/>
     </row>
-    <row r="378" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A378" s="6" t="s">
         <v>30</v>
       </c>
@@ -32027,7 +32015,7 @@
       <c r="AD378" s="7"/>
       <c r="AE378" s="8"/>
     </row>
-    <row r="379" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A379" s="6" t="s">
         <v>30</v>
       </c>
@@ -32100,7 +32088,7 @@
       <c r="AD379" s="7"/>
       <c r="AE379" s="8"/>
     </row>
-    <row r="380" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A380" s="6" t="s">
         <v>30</v>
       </c>
@@ -32173,7 +32161,7 @@
       <c r="AD380" s="7"/>
       <c r="AE380" s="8"/>
     </row>
-    <row r="381" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A381" s="6" t="s">
         <v>30</v>
       </c>
@@ -32246,7 +32234,7 @@
       <c r="AD381" s="7"/>
       <c r="AE381" s="8"/>
     </row>
-    <row r="382" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A382" s="6" t="s">
         <v>30</v>
       </c>
@@ -32319,7 +32307,7 @@
       <c r="AD382" s="7"/>
       <c r="AE382" s="8"/>
     </row>
-    <row r="383" spans="1:31" ht="29" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A383" s="6" t="s">
         <v>30</v>
       </c>
@@ -32332,16 +32320,16 @@
       <c r="D383" s="6" t="s">
         <v>1204</v>
       </c>
-      <c r="E383" s="9" t="s">
+      <c r="E383" s="6" t="s">
         <v>428</v>
       </c>
-      <c r="F383" s="9" t="s">
+      <c r="F383" s="6" t="s">
         <v>1205</v>
       </c>
       <c r="G383" s="6" t="s">
         <v>1206</v>
       </c>
-      <c r="H383" s="9" t="s">
+      <c r="H383" s="6" t="s">
         <v>1205</v>
       </c>
       <c r="I383" s="6">
@@ -32387,14 +32375,16 @@
       </c>
       <c r="AB383" s="6"/>
       <c r="AC383" s="7">
-        <v>232.5</v>
-      </c>
-      <c r="AD383" s="7"/>
+        <v>0</v>
+      </c>
+      <c r="AD383" s="7" t="s">
+        <v>1216</v>
+      </c>
       <c r="AE383" s="8" t="s">
-        <v>1225</v>
-      </c>
-    </row>
-    <row r="384" spans="1:31" x14ac:dyDescent="0.35">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="384" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A384" s="6" t="s">
         <v>30</v>
       </c>
@@ -32407,16 +32397,16 @@
       <c r="D384" s="6" t="s">
         <v>1204</v>
       </c>
-      <c r="E384" s="9" t="s">
+      <c r="E384" s="6" t="s">
         <v>428</v>
       </c>
-      <c r="F384" s="9" t="s">
+      <c r="F384" s="6" t="s">
         <v>1208</v>
       </c>
       <c r="G384" s="6" t="s">
         <v>1206</v>
       </c>
-      <c r="H384" s="9" t="s">
+      <c r="H384" s="6" t="s">
         <v>1205</v>
       </c>
       <c r="I384" s="6">
@@ -32467,7 +32457,7 @@
       <c r="AD384" s="7"/>
       <c r="AE384" s="8"/>
     </row>
-    <row r="385" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A385" s="6" t="s">
         <v>30</v>
       </c>
@@ -32480,16 +32470,16 @@
       <c r="D385" s="6" t="s">
         <v>1204</v>
       </c>
-      <c r="E385" s="9" t="s">
+      <c r="E385" s="6" t="s">
         <v>428</v>
       </c>
-      <c r="F385" s="9" t="s">
+      <c r="F385" s="6" t="s">
         <v>1210</v>
       </c>
       <c r="G385" s="6" t="s">
         <v>1206</v>
       </c>
-      <c r="H385" s="9" t="s">
+      <c r="H385" s="6" t="s">
         <v>1205</v>
       </c>
       <c r="I385" s="6">
@@ -32540,7 +32530,7 @@
       <c r="AD385" s="7"/>
       <c r="AE385" s="8"/>
     </row>
-    <row r="386" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A386" s="6" t="s">
         <v>30</v>
       </c>
@@ -32612,11 +32602,7 @@
       <c r="AE386" s="8"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AE386" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A109:AE125">
-      <sortCondition ref="E1:E386"/>
-    </sortState>
-  </autoFilter>
+  <autoFilter ref="A1:AE386" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -32839,10 +32825,16 @@
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DB7C548F-0683-4FD3-86CB-C58F9C3DA88F}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="a27a8b09-69d1-4ac5-96a8-2f85c0adea8e"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="fac624ca-f647-4614-b3e1-01738629c215"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="fac624ca-f647-4614-b3e1-01738629c215"/>
-    <ds:schemaRef ds:uri="a27a8b09-69d1-4ac5-96a8-2f85c0adea8e"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
